--- a/site/ADP-Workforce-Now-to-Microsoft-Entra-ID-Integration-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-to-Microsoft-Entra-ID-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -908,7 +908,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -991,7 +991,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Log Insights Settings</t>
+          <t>Success Notification Settings</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1001,63 +1001,63 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KJBZZH5XZG9CGR1VQ8SGBP6R</t>
+          <t>h_01KMFQQJRR6ZVVR1AYCHWZGHSQ</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-Integration-Guide/#h_01KJBZZH5XZG9CGR1VQ8SGBP6R</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-Integration-Guide/#h_01KMFQQJRR6ZVVR1AYCHWZGHSQ</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Failure Notification Settings</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KJBZZQGVD2CX5G52BN7Z2W0F</t>
+          <t>h_01KMFQQSQ57H477YC8CRBGHW6S</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-Integration-Guide/#h_01KJBZZQGVD2CX5G52BN7Z2W0F</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-Integration-Guide/#h_01KMFQQSQ57H477YC8CRBGHW6S</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ADP Workforce Now Worker Group Assignment Rules</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01KKK905A6C5B27XQ1TP2S6PW4</t>
+          <t>h_01KMFQQYDHMNDF5BZH8SEX0P9G</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-Integration-Guide/#h_01KKK905A6C5B27XQ1TP2S6PW4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-Integration-Guide/#h_01KMFQQYDHMNDF5BZH8SEX0P9G</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Remove Groups on Deactivation</t>
+          <t>Log Insights Settings</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1067,19 +1067,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01KKK905A7MB4SD9FAKFFVFMF9</t>
+          <t>h_01KJBZZH5XZG9CGR1VQ8SGBP6R</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-Integration-Guide/#h_01KKK905A7MB4SD9FAKFFVFMF9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-Integration-Guide/#h_01KJBZZH5XZG9CGR1VQ8SGBP6R</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Group Assignment Rules</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1089,41 +1089,41 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01KKK905A7JKH88XH3K9B5HF7G</t>
+          <t>h_01KJBZZQGVD2CX5G52BN7Z2W0F</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-Integration-Guide/#h_01KKK905A7JKH88XH3K9B5HF7G</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-Integration-Guide/#h_01KJBZZQGVD2CX5G52BN7Z2W0F</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Example</t>
+          <t>ADP Workforce Now Worker Group Assignment Rules</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01KKK905AA86CK7HFVVSHYT47Q</t>
+          <t>h_01KKK905A6C5B27XQ1TP2S6PW4</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-Integration-Guide/#h_01KKK905AA86CK7HFVVSHYT47Q</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-Integration-Guide/#h_01KKK905A6C5B27XQ1TP2S6PW4</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Using a Different Attribute</t>
+          <t>Remove Groups on Deactivation</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1133,19 +1133,19 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01KKK905ADADNWSNAKWR8EM0XH</t>
+          <t>h_01KKK905A7MB4SD9FAKFFVFMF9</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-Integration-Guide/#h_01KKK905ADADNWSNAKWR8EM0XH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-Integration-Guide/#h_01KKK905A7MB4SD9FAKFFVFMF9</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Expression Mode</t>
+          <t>Group Assignment Rules</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1155,98 +1155,164 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>h_01KKK905ADYEGNJHAWDGRV105G</t>
+          <t>h_01KKK905A7JKH88XH3K9B5HF7G</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-Integration-Guide/#h_01KKK905ADYEGNJHAWDGRV105G</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-Integration-Guide/#h_01KKK905A7JKH88XH3K9B5HF7G</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Example</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KKK905AA86CK7HFVVSHYT47Q</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-Integration-Guide/#h_01KKK905AA86CK7HFVVSHYT47Q</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Using a Different Attribute</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KKK905ADADNWSNAKWR8EM0XH</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-Integration-Guide/#h_01KKK905ADADNWSNAKWR8EM0XH</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Expression Mode</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01KKK905ADYEGNJHAWDGRV105G</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-Integration-Guide/#h_01KKK905ADYEGNJHAWDGRV105G</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
